--- a/backend/data/financials_by_company/1DEZ.MI.xlsx
+++ b/backend/data/financials_by_company/1DEZ.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA5"/>
+  <dimension ref="A1:BA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,217 +687,129 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D2" t="n">
-        <v>149500000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>200000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>104100000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1412900000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>149700000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>45600000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-17200000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>20900000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>41830000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>51800000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1777900000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>132420000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>132420000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="W2" t="n">
-        <v>51800000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>51800000</v>
-      </c>
-      <c r="Y2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="n">
+        <v>37200000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>51800000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>51800000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>42000000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-17300000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>24700000</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="n">
+        <v>3100000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
         <v>700000</v>
       </c>
-      <c r="AH2" t="n">
-        <v>-900000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>200000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="n">
-        <v>-17200000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>20900000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>35800000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>365000000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>14900000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>23400000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>23400000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>100400000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>81700000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>39800000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>41900000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>400800000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1412900000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1813700000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>1813700000</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>12000</v>
+        <v>-645000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.012</v>
+        <v>0.15</v>
       </c>
       <c r="D3" t="n">
-        <v>232300000</v>
+        <v>195900000</v>
       </c>
       <c r="E3" t="n">
-        <v>1000000</v>
+        <v>-4300000</v>
       </c>
       <c r="F3" t="n">
-        <v>1000000</v>
+        <v>-4300000</v>
       </c>
       <c r="G3" t="n">
-        <v>106900000</v>
+        <v>95400000</v>
       </c>
       <c r="H3" t="n">
-        <v>108700000</v>
+        <v>93600000</v>
       </c>
       <c r="I3" t="n">
-        <v>1616400000</v>
+        <v>1524500000</v>
       </c>
       <c r="J3" t="n">
-        <v>233300000</v>
+        <v>191600000</v>
       </c>
       <c r="K3" t="n">
-        <v>124600000</v>
+        <v>98000000</v>
       </c>
       <c r="L3" t="n">
-        <v>-15300000</v>
+        <v>-5900000</v>
       </c>
       <c r="M3" t="n">
-        <v>16400000</v>
+        <v>6300000</v>
       </c>
       <c r="N3" t="n">
-        <v>1800000</v>
+        <v>1300000</v>
       </c>
       <c r="O3" t="n">
-        <v>105912000</v>
+        <v>99055000</v>
       </c>
       <c r="P3" t="n">
-        <v>81900000</v>
+        <v>80200000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1931300000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>1787900000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>89400000</v>
+      </c>
       <c r="S3" t="n">
-        <v>124902000</v>
+        <v>120862000</v>
       </c>
       <c r="T3" t="n">
-        <v>124902000</v>
+        <v>120862000</v>
       </c>
       <c r="U3" t="n">
         <v>0.66</v>
@@ -906,157 +818,157 @@
         <v>0.66</v>
       </c>
       <c r="W3" t="n">
-        <v>81900000</v>
+        <v>80200000</v>
       </c>
       <c r="X3" t="n">
-        <v>81900000</v>
+        <v>80200000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>81900000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
+        <v>80200000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
       <c r="AB3" t="n">
-        <v>81900000</v>
+        <v>80200000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-25000000</v>
+        <v>-15200000</v>
       </c>
       <c r="AD3" t="n">
-        <v>106900000</v>
+        <v>95400000</v>
       </c>
       <c r="AE3" t="n">
+        <v>-3700000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>91700000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-4300000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-500000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-5900000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>900000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>6300000</v>
+      </c>
+      <c r="AN3" t="n">
         <v>1300000</v>
       </c>
-      <c r="AF3" t="n">
-        <v>108200000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>700000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>-300000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-400000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>-15300000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>700000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>16400000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1800000</v>
-      </c>
       <c r="AO3" t="n">
-        <v>131900000</v>
+        <v>104200000</v>
       </c>
       <c r="AP3" t="n">
-        <v>314900000</v>
+        <v>263400000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>600000</v>
+        <v>-600000</v>
       </c>
       <c r="AR3" t="n">
-        <v>16300000</v>
+        <v>13200000</v>
       </c>
       <c r="AS3" t="n">
-        <v>16300000</v>
+        <v>13200000</v>
       </c>
       <c r="AT3" t="n">
-        <v>109600000</v>
+        <v>97500000</v>
       </c>
       <c r="AU3" t="n">
-        <v>67100000</v>
+        <v>42000000</v>
       </c>
       <c r="AV3" t="n">
-        <v>44900000</v>
+        <v>32100000</v>
       </c>
       <c r="AW3" t="n">
-        <v>22200000</v>
+        <v>9900000</v>
       </c>
       <c r="AX3" t="n">
-        <v>446800000</v>
+        <v>367600000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1616400000</v>
+        <v>1524500000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2063200000</v>
+        <v>1892100000</v>
       </c>
       <c r="BA3" t="n">
-        <v>2063200000</v>
+        <v>1892100000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-645000</v>
+        <v>12000</v>
       </c>
       <c r="C4" t="n">
-        <v>0.15</v>
+        <v>0.012</v>
       </c>
       <c r="D4" t="n">
-        <v>195900000</v>
+        <v>232300000</v>
       </c>
       <c r="E4" t="n">
-        <v>-4300000</v>
+        <v>1000000</v>
       </c>
       <c r="F4" t="n">
-        <v>-4300000</v>
+        <v>1000000</v>
       </c>
       <c r="G4" t="n">
-        <v>95400000</v>
+        <v>106900000</v>
       </c>
       <c r="H4" t="n">
-        <v>93600000</v>
+        <v>108700000</v>
       </c>
       <c r="I4" t="n">
-        <v>1524500000</v>
+        <v>1616400000</v>
       </c>
       <c r="J4" t="n">
-        <v>191600000</v>
+        <v>233300000</v>
       </c>
       <c r="K4" t="n">
-        <v>98000000</v>
+        <v>124600000</v>
       </c>
       <c r="L4" t="n">
-        <v>-5900000</v>
+        <v>-15300000</v>
       </c>
       <c r="M4" t="n">
-        <v>6300000</v>
+        <v>16400000</v>
       </c>
       <c r="N4" t="n">
-        <v>1300000</v>
+        <v>1800000</v>
       </c>
       <c r="O4" t="n">
-        <v>99055000</v>
+        <v>105912000</v>
       </c>
       <c r="P4" t="n">
-        <v>80200000</v>
+        <v>81900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1787900000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>89400000</v>
-      </c>
+        <v>1931300000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>120862000</v>
+        <v>124902000</v>
       </c>
       <c r="T4" t="n">
-        <v>120862000</v>
+        <v>124902000</v>
       </c>
       <c r="U4" t="n">
         <v>0.66</v>
@@ -1065,256 +977,407 @@
         <v>0.66</v>
       </c>
       <c r="W4" t="n">
-        <v>80200000</v>
+        <v>81900000</v>
       </c>
       <c r="X4" t="n">
-        <v>80200000</v>
+        <v>81900000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>80200000</v>
-      </c>
-      <c r="AA4" t="n">
+        <v>81900000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="n">
+        <v>81900000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-25000000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>106900000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>108200000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>700000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-300000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-400000</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" t="n">
-        <v>80200000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-15200000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>95400000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-3700000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>91700000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>-4300000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-500000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>400000</v>
-      </c>
       <c r="AK4" t="n">
-        <v>-5900000</v>
+        <v>-15300000</v>
       </c>
       <c r="AL4" t="n">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="AM4" t="n">
-        <v>6300000</v>
+        <v>16400000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1300000</v>
+        <v>1800000</v>
       </c>
       <c r="AO4" t="n">
-        <v>104200000</v>
+        <v>131900000</v>
       </c>
       <c r="AP4" t="n">
-        <v>263400000</v>
+        <v>314900000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-600000</v>
+        <v>600000</v>
       </c>
       <c r="AR4" t="n">
-        <v>13200000</v>
+        <v>16300000</v>
       </c>
       <c r="AS4" t="n">
-        <v>13200000</v>
+        <v>16300000</v>
       </c>
       <c r="AT4" t="n">
-        <v>97500000</v>
+        <v>109600000</v>
       </c>
       <c r="AU4" t="n">
-        <v>42000000</v>
+        <v>67100000</v>
       </c>
       <c r="AV4" t="n">
-        <v>32100000</v>
+        <v>44900000</v>
       </c>
       <c r="AW4" t="n">
-        <v>9900000</v>
+        <v>22200000</v>
       </c>
       <c r="AX4" t="n">
-        <v>367600000</v>
+        <v>446800000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1524500000</v>
+        <v>1616400000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1892100000</v>
+        <v>2063200000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1892100000</v>
+        <v>2063200000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-870000</v>
+        <v>30000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D5" t="n">
-        <v>126200000</v>
+        <v>149500000</v>
       </c>
       <c r="E5" t="n">
-        <v>-2900000</v>
+        <v>200000</v>
       </c>
       <c r="F5" t="n">
-        <v>-2900000</v>
+        <v>200000</v>
       </c>
       <c r="G5" t="n">
-        <v>38200000</v>
+        <v>42000000</v>
       </c>
       <c r="H5" t="n">
-        <v>89000000</v>
+        <v>104100000</v>
       </c>
       <c r="I5" t="n">
-        <v>1344800000</v>
+        <v>1412900000</v>
       </c>
       <c r="J5" t="n">
-        <v>123300000</v>
+        <v>149700000</v>
       </c>
       <c r="K5" t="n">
-        <v>34300000</v>
+        <v>45600000</v>
       </c>
       <c r="L5" t="n">
-        <v>-5000000</v>
+        <v>-17200000</v>
       </c>
       <c r="M5" t="n">
-        <v>5200000</v>
+        <v>20900000</v>
       </c>
       <c r="N5" t="n">
-        <v>200000</v>
+        <v>2400000</v>
       </c>
       <c r="O5" t="n">
-        <v>40230000</v>
+        <v>41830000</v>
       </c>
       <c r="P5" t="n">
-        <v>38200000</v>
+        <v>51800000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1588000000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>37200000</v>
-      </c>
+        <v>1777900000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>120861783</v>
+        <v>132420000</v>
       </c>
       <c r="T5" t="n">
-        <v>120861783</v>
+        <v>132420000</v>
       </c>
       <c r="U5" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="V5" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="W5" t="n">
-        <v>38200000</v>
+        <v>51800000</v>
       </c>
       <c r="X5" t="n">
-        <v>38200000</v>
+        <v>51800000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>38200000</v>
+        <v>51800000</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>38200000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
+        <v>51800000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9800000</v>
+      </c>
       <c r="AD5" t="n">
-        <v>38200000</v>
+        <v>42000000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-9100000</v>
+        <v>-17300000</v>
       </c>
       <c r="AF5" t="n">
-        <v>29100000</v>
+        <v>24700000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2600000</v>
+        <v>700000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-700000</v>
+        <v>-900000</v>
       </c>
       <c r="AI5" t="n">
         <v>200000</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>3100000</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>-5000000</v>
+        <v>-17200000</v>
       </c>
       <c r="AL5" t="n">
-        <v>700000</v>
+        <v>-1300000</v>
       </c>
       <c r="AM5" t="n">
-        <v>5200000</v>
+        <v>20900000</v>
       </c>
       <c r="AN5" t="n">
-        <v>200000</v>
+        <v>2400000</v>
       </c>
       <c r="AO5" t="n">
-        <v>29300000</v>
+        <v>35800000</v>
       </c>
       <c r="AP5" t="n">
-        <v>243200000</v>
+        <v>365000000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12300000</v>
+        <v>14900000</v>
       </c>
       <c r="AR5" t="n">
-        <v>20800000</v>
+        <v>23400000</v>
       </c>
       <c r="AS5" t="n">
-        <v>20800000</v>
+        <v>23400000</v>
       </c>
       <c r="AT5" t="n">
+        <v>100400000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>81700000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>39800000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>41900000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>400800000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1412900000</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1813700000</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1813700000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>63619.744059</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.010969</v>
+      </c>
+      <c r="D6" t="n">
+        <v>164800000</v>
+      </c>
+      <c r="E6" t="n">
         <v>5800000</v>
       </c>
-      <c r="AU5" t="n">
-        <v>164800000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>103200000</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>61600000</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>272500000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1344800000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1617300000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1617300000</v>
+      <c r="F6" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>53600000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>95700000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1604400000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>170600000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>74900000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-19200000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20200000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>47863619.744059</v>
+      </c>
+      <c r="P6" t="n">
+        <v>53600000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1981600000</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>143096000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>143096000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="W6" t="n">
+        <v>53600000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>53600000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>53600000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>54100000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>54100000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>54700000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>-19200000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>20200000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>62200000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>377200000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>29700000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>29700000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>94100000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>84400000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>48700000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>35700000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>439400000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1604400000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2043800000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>2043800000</v>
       </c>
     </row>
   </sheetData>
@@ -1328,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BR5"/>
+  <dimension ref="A1:BR6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,836 +1743,916 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>138761914</v>
-      </c>
-      <c r="C2" t="n">
-        <v>138761914</v>
-      </c>
-      <c r="D2" t="n">
-        <v>138700000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>287600000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>544900000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1048600000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>171500000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>544900000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>86900000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>847900000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>919500000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>847900000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>847900000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>421100000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>78900000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>354700000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>354700000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>835400000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>261100000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>77300000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>5600000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>131700000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>60100000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>71600000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>26500000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>574300000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>89600000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>155900000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>26800000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>129100000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>9800000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>82500000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>236500000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>235000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1683300000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>937500000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>10800000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>153900000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6300000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>6300000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>43800000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>303000000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>221300000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>81700000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>418400000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-973500000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>1391900000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>37600000</v>
-      </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>1012700000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>341600000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>745800000</v>
-      </c>
-      <c r="BE2" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>6800000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>431600000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>130000000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>239600000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>29100000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>29500000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>186800000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>-5600000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>192400000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>62000000</v>
-      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>368500000</v>
+      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>126147195</v>
+        <v>120861783</v>
       </c>
       <c r="C3" t="n">
-        <v>126147195</v>
+        <v>120861783</v>
       </c>
       <c r="D3" t="n">
-        <v>81900000</v>
+        <v>69600000</v>
       </c>
       <c r="E3" t="n">
-        <v>253500000</v>
+        <v>219100000</v>
       </c>
       <c r="F3" t="n">
-        <v>583300000</v>
+        <v>499500000</v>
       </c>
       <c r="G3" t="n">
-        <v>915200000</v>
+        <v>793300000</v>
       </c>
       <c r="H3" t="n">
-        <v>211400000</v>
+        <v>134300000</v>
       </c>
       <c r="I3" t="n">
-        <v>583300000</v>
+        <v>499500000</v>
       </c>
       <c r="J3" t="n">
-        <v>81500000</v>
+        <v>94600000</v>
       </c>
       <c r="K3" t="n">
-        <v>743200000</v>
+        <v>668800000</v>
       </c>
       <c r="L3" t="n">
-        <v>743500000</v>
+        <v>669200000</v>
       </c>
       <c r="M3" t="n">
-        <v>743200000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>668800000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>743200000</v>
+        <v>668800000</v>
       </c>
       <c r="P3" t="n">
-        <v>387100000</v>
+        <v>330400000</v>
       </c>
       <c r="Q3" t="n">
-        <v>40300000</v>
+        <v>28800000</v>
       </c>
       <c r="R3" t="n">
-        <v>322500000</v>
+        <v>309000000</v>
       </c>
       <c r="S3" t="n">
-        <v>322500000</v>
+        <v>309000000</v>
       </c>
       <c r="T3" t="n">
-        <v>847000000</v>
+        <v>806600000</v>
       </c>
       <c r="U3" t="n">
-        <v>202900000</v>
+        <v>195800000</v>
       </c>
       <c r="V3" t="n">
-        <v>19600000</v>
+        <v>2200000</v>
       </c>
       <c r="W3" t="n">
-        <v>87700000</v>
+        <v>86000000</v>
       </c>
       <c r="X3" t="n">
-        <v>5800000</v>
+        <v>2000000</v>
       </c>
       <c r="Y3" t="n">
-        <v>65900000</v>
+        <v>77200000</v>
       </c>
       <c r="Z3" t="n">
-        <v>65600000</v>
+        <v>76800000</v>
       </c>
       <c r="AA3" t="n">
-        <v>300000</v>
+        <v>400000</v>
       </c>
       <c r="AB3" t="n">
-        <v>23900000</v>
+        <v>28400000</v>
       </c>
       <c r="AC3" t="n">
-        <v>644100000</v>
+        <v>610800000</v>
       </c>
       <c r="AD3" t="n">
-        <v>90600000</v>
+        <v>79700000</v>
       </c>
       <c r="AE3" t="n">
-        <v>187600000</v>
+        <v>141900000</v>
       </c>
       <c r="AF3" t="n">
-        <v>15900000</v>
+        <v>17800000</v>
       </c>
       <c r="AG3" t="n">
-        <v>171700000</v>
+        <v>124100000</v>
       </c>
       <c r="AH3" t="n">
-        <v>10700000</v>
+        <v>11100000</v>
       </c>
       <c r="AI3" t="n">
-        <v>73800000</v>
+        <v>81700000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>262400000</v>
+        <v>296400000</v>
       </c>
       <c r="AK3" t="n">
-        <v>6400000</v>
+        <v>4900000</v>
       </c>
       <c r="AL3" t="n">
-        <v>256000000</v>
+        <v>291500000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1590200000</v>
+        <v>1475400000</v>
       </c>
       <c r="AN3" t="n">
-        <v>734700000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>13000000</v>
-      </c>
+        <v>730300000</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="n">
-        <v>127400000</v>
+        <v>101300000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13700000</v>
+        <v>14400000</v>
       </c>
       <c r="AR3" t="n">
-        <v>13700000</v>
+        <v>14400000</v>
       </c>
       <c r="AS3" t="n">
-        <v>41400000</v>
+        <v>50600000</v>
       </c>
       <c r="AT3" t="n">
-        <v>159900000</v>
+        <v>169300000</v>
       </c>
       <c r="AU3" t="n">
-        <v>121900000</v>
+        <v>113800000</v>
       </c>
       <c r="AV3" t="n">
-        <v>38000000</v>
+        <v>55500000</v>
       </c>
       <c r="AW3" t="n">
-        <v>379300000</v>
+        <v>394700000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-930300000</v>
+        <v>-904700000</v>
       </c>
       <c r="AY3" t="n">
-        <v>1309600000</v>
+        <v>1299400000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18200000</v>
-      </c>
-      <c r="BA3" t="inlineStr"/>
+        <v>22200000</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>371900000</v>
+      </c>
       <c r="BB3" t="n">
-        <v>964900000</v>
+        <v>944300000</v>
       </c>
       <c r="BC3" t="n">
-        <v>326500000</v>
+        <v>332900000</v>
       </c>
       <c r="BD3" t="n">
-        <v>855500000</v>
+        <v>745100000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1500000</v>
+        <v>800000</v>
       </c>
       <c r="BF3" t="n">
-        <v>75700000</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
-        <v>5800000</v>
+        <v>4100000</v>
       </c>
       <c r="BH3" t="n">
-        <v>433900000</v>
+        <v>451600000</v>
       </c>
       <c r="BI3" t="n">
-        <v>128900000</v>
+        <v>127300000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>56100000</v>
+        <v>49900000</v>
       </c>
       <c r="BK3" t="n">
-        <v>248900000</v>
+        <v>274400000</v>
       </c>
       <c r="BL3" t="n">
-        <v>30600000</v>
+        <v>33500000</v>
       </c>
       <c r="BM3" t="n">
-        <v>15500000</v>
+        <v>12500000</v>
       </c>
       <c r="BN3" t="n">
-        <v>202400000</v>
+        <v>187700000</v>
       </c>
       <c r="BO3" t="n">
-        <v>-5400000</v>
+        <v>-9900000</v>
       </c>
       <c r="BP3" t="n">
-        <v>207800000</v>
+        <v>197600000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>90100000</v>
+        <v>54900000</v>
       </c>
       <c r="BR3" t="n">
-        <v>90100000</v>
+        <v>54900000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>120861783</v>
+        <v>126147195</v>
       </c>
       <c r="C4" t="n">
-        <v>120861783</v>
+        <v>126147195</v>
       </c>
       <c r="D4" t="n">
-        <v>69600000</v>
+        <v>81900000</v>
       </c>
       <c r="E4" t="n">
-        <v>219100000</v>
+        <v>253500000</v>
       </c>
       <c r="F4" t="n">
-        <v>499500000</v>
+        <v>583300000</v>
       </c>
       <c r="G4" t="n">
-        <v>793300000</v>
+        <v>915200000</v>
       </c>
       <c r="H4" t="n">
-        <v>134300000</v>
+        <v>211400000</v>
       </c>
       <c r="I4" t="n">
-        <v>499500000</v>
+        <v>583300000</v>
       </c>
       <c r="J4" t="n">
-        <v>94600000</v>
+        <v>81500000</v>
       </c>
       <c r="K4" t="n">
-        <v>668800000</v>
+        <v>743200000</v>
       </c>
       <c r="L4" t="n">
-        <v>669200000</v>
+        <v>743500000</v>
       </c>
       <c r="M4" t="n">
-        <v>668800000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
+        <v>743200000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>668800000</v>
+        <v>743200000</v>
       </c>
       <c r="P4" t="n">
-        <v>330400000</v>
+        <v>387100000</v>
       </c>
       <c r="Q4" t="n">
-        <v>28800000</v>
+        <v>40300000</v>
       </c>
       <c r="R4" t="n">
-        <v>309000000</v>
+        <v>322500000</v>
       </c>
       <c r="S4" t="n">
-        <v>309000000</v>
+        <v>322500000</v>
       </c>
       <c r="T4" t="n">
-        <v>806600000</v>
+        <v>847000000</v>
       </c>
       <c r="U4" t="n">
-        <v>195800000</v>
+        <v>202900000</v>
       </c>
       <c r="V4" t="n">
-        <v>2200000</v>
+        <v>19600000</v>
       </c>
       <c r="W4" t="n">
-        <v>86000000</v>
+        <v>87700000</v>
       </c>
       <c r="X4" t="n">
-        <v>2000000</v>
+        <v>5800000</v>
       </c>
       <c r="Y4" t="n">
-        <v>77200000</v>
+        <v>65900000</v>
       </c>
       <c r="Z4" t="n">
-        <v>76800000</v>
+        <v>65600000</v>
       </c>
       <c r="AA4" t="n">
-        <v>400000</v>
+        <v>300000</v>
       </c>
       <c r="AB4" t="n">
-        <v>28400000</v>
+        <v>23900000</v>
       </c>
       <c r="AC4" t="n">
-        <v>610800000</v>
+        <v>644100000</v>
       </c>
       <c r="AD4" t="n">
-        <v>79700000</v>
+        <v>90600000</v>
       </c>
       <c r="AE4" t="n">
-        <v>141900000</v>
+        <v>187600000</v>
       </c>
       <c r="AF4" t="n">
-        <v>17800000</v>
+        <v>15900000</v>
       </c>
       <c r="AG4" t="n">
-        <v>124100000</v>
+        <v>171700000</v>
       </c>
       <c r="AH4" t="n">
-        <v>11100000</v>
+        <v>10700000</v>
       </c>
       <c r="AI4" t="n">
-        <v>81700000</v>
+        <v>73800000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>296400000</v>
+        <v>262400000</v>
       </c>
       <c r="AK4" t="n">
-        <v>4900000</v>
+        <v>6400000</v>
       </c>
       <c r="AL4" t="n">
-        <v>291500000</v>
+        <v>256000000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1475400000</v>
+        <v>1590200000</v>
       </c>
       <c r="AN4" t="n">
-        <v>730300000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
+        <v>734700000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>13000000</v>
+      </c>
       <c r="AP4" t="n">
-        <v>101300000</v>
+        <v>127400000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14400000</v>
+        <v>13700000</v>
       </c>
       <c r="AR4" t="n">
-        <v>14400000</v>
+        <v>13700000</v>
       </c>
       <c r="AS4" t="n">
-        <v>50600000</v>
+        <v>41400000</v>
       </c>
       <c r="AT4" t="n">
-        <v>169300000</v>
+        <v>159900000</v>
       </c>
       <c r="AU4" t="n">
-        <v>113800000</v>
+        <v>121900000</v>
       </c>
       <c r="AV4" t="n">
-        <v>55500000</v>
+        <v>38000000</v>
       </c>
       <c r="AW4" t="n">
-        <v>394700000</v>
+        <v>379300000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-904700000</v>
+        <v>-930300000</v>
       </c>
       <c r="AY4" t="n">
-        <v>1299400000</v>
+        <v>1309600000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22200000</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>371900000</v>
-      </c>
+        <v>18200000</v>
+      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>944300000</v>
+        <v>964900000</v>
       </c>
       <c r="BC4" t="n">
-        <v>332900000</v>
+        <v>326500000</v>
       </c>
       <c r="BD4" t="n">
-        <v>745100000</v>
+        <v>855500000</v>
       </c>
       <c r="BE4" t="n">
-        <v>800000</v>
+        <v>1500000</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>75700000</v>
       </c>
       <c r="BG4" t="n">
-        <v>4100000</v>
+        <v>5800000</v>
       </c>
       <c r="BH4" t="n">
-        <v>451600000</v>
+        <v>433900000</v>
       </c>
       <c r="BI4" t="n">
-        <v>127300000</v>
+        <v>128900000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>49900000</v>
+        <v>56100000</v>
       </c>
       <c r="BK4" t="n">
-        <v>274400000</v>
+        <v>248900000</v>
       </c>
       <c r="BL4" t="n">
-        <v>33500000</v>
+        <v>30600000</v>
       </c>
       <c r="BM4" t="n">
-        <v>12500000</v>
+        <v>15500000</v>
       </c>
       <c r="BN4" t="n">
-        <v>187700000</v>
+        <v>202400000</v>
       </c>
       <c r="BO4" t="n">
-        <v>-9900000</v>
+        <v>-5400000</v>
       </c>
       <c r="BP4" t="n">
-        <v>197600000</v>
+        <v>207800000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>54900000</v>
+        <v>90100000</v>
       </c>
       <c r="BR4" t="n">
-        <v>54900000</v>
+        <v>90100000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>120861783</v>
+        <v>138761914</v>
       </c>
       <c r="C5" t="n">
-        <v>120861783</v>
+        <v>138761914</v>
       </c>
       <c r="D5" t="n">
-        <v>18400000</v>
+        <v>138700000</v>
       </c>
       <c r="E5" t="n">
-        <v>115800000</v>
+        <v>287600000</v>
       </c>
       <c r="F5" t="n">
-        <v>406600000</v>
+        <v>544900000</v>
       </c>
       <c r="G5" t="n">
-        <v>642900000</v>
+        <v>1048600000</v>
       </c>
       <c r="H5" t="n">
-        <v>106300000</v>
+        <v>171900000</v>
       </c>
       <c r="I5" t="n">
-        <v>406600000</v>
+        <v>544900000</v>
       </c>
       <c r="J5" t="n">
-        <v>61300000</v>
+        <v>86900000</v>
       </c>
       <c r="K5" t="n">
-        <v>588400000</v>
+        <v>847900000</v>
       </c>
       <c r="L5" t="n">
-        <v>592200000</v>
+        <v>919500000</v>
       </c>
       <c r="M5" t="n">
-        <v>588400000</v>
+        <v>847900000</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>588400000</v>
+        <v>847900000</v>
       </c>
       <c r="P5" t="n">
-        <v>246900000</v>
+        <v>421100000</v>
       </c>
       <c r="Q5" t="n">
-        <v>28800000</v>
+        <v>78900000</v>
       </c>
       <c r="R5" t="n">
-        <v>309000000</v>
+        <v>354700000</v>
       </c>
       <c r="S5" t="n">
-        <v>309000000</v>
+        <v>354700000</v>
       </c>
       <c r="T5" t="n">
-        <v>701700000</v>
+        <v>835800000</v>
       </c>
       <c r="U5" t="n">
-        <v>214700000</v>
+        <v>261500000</v>
       </c>
       <c r="V5" t="n">
-        <v>3600000</v>
+        <v>20400000</v>
       </c>
       <c r="W5" t="n">
-        <v>126700000</v>
+        <v>77300000</v>
       </c>
       <c r="X5" t="n">
-        <v>1800000</v>
+        <v>5600000</v>
       </c>
       <c r="Y5" t="n">
-        <v>49200000</v>
+        <v>131700000</v>
       </c>
       <c r="Z5" t="n">
-        <v>45400000</v>
+        <v>60100000</v>
       </c>
       <c r="AA5" t="n">
-        <v>3800000</v>
+        <v>71600000</v>
       </c>
       <c r="AB5" t="n">
-        <v>33400000</v>
+        <v>26500000</v>
       </c>
       <c r="AC5" t="n">
-        <v>487000000</v>
+        <v>574300000</v>
       </c>
       <c r="AD5" t="n">
-        <v>62900000</v>
+        <v>89600000</v>
       </c>
       <c r="AE5" t="n">
-        <v>66600000</v>
+        <v>155900000</v>
       </c>
       <c r="AF5" t="n">
-        <v>15900000</v>
+        <v>26800000</v>
       </c>
       <c r="AG5" t="n">
-        <v>50700000</v>
+        <v>129100000</v>
       </c>
       <c r="AH5" t="n">
-        <v>11100000</v>
+        <v>9800000</v>
       </c>
       <c r="AI5" t="n">
-        <v>85600000</v>
+        <v>82500000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>260800000</v>
+        <v>236500000</v>
       </c>
       <c r="AK5" t="n">
-        <v>3000000</v>
+        <v>1500000</v>
       </c>
       <c r="AL5" t="n">
-        <v>257800000</v>
+        <v>235000000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1290100000</v>
+        <v>1683700000</v>
       </c>
       <c r="AN5" t="n">
-        <v>696800000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
+        <v>937500000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>10800000</v>
+      </c>
       <c r="AP5" t="n">
-        <v>88600000</v>
+        <v>153900000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11100000</v>
+        <v>6300000</v>
       </c>
       <c r="AR5" t="n">
-        <v>11100000</v>
+        <v>6300000</v>
       </c>
       <c r="AS5" t="n">
-        <v>56400000</v>
+        <v>43800000</v>
       </c>
       <c r="AT5" t="n">
-        <v>181800000</v>
+        <v>303000000</v>
       </c>
       <c r="AU5" t="n">
-        <v>127500000</v>
+        <v>221300000</v>
       </c>
       <c r="AV5" t="n">
-        <v>54300000</v>
+        <v>81700000</v>
       </c>
       <c r="AW5" t="n">
-        <v>358900000</v>
+        <v>418400000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-899600000</v>
+        <v>-973500000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1258500000</v>
+        <v>1391900000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>18300000</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>368500000</v>
-      </c>
+        <v>37600000</v>
+      </c>
+      <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>945700000</v>
+        <v>1012700000</v>
       </c>
       <c r="BC5" t="n">
-        <v>294500000</v>
+        <v>341600000</v>
       </c>
       <c r="BD5" t="n">
-        <v>593300000</v>
+        <v>746200000</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
       <c r="BG5" t="n">
-        <v>3600000</v>
+        <v>6800000</v>
       </c>
       <c r="BH5" t="n">
-        <v>375300000</v>
+        <v>431600000</v>
       </c>
       <c r="BI5" t="n">
-        <v>106600000</v>
+        <v>130000000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>44200000</v>
+        <v>62000000</v>
       </c>
       <c r="BK5" t="n">
-        <v>224500000</v>
+        <v>239600000</v>
       </c>
       <c r="BL5" t="n">
-        <v>22700000</v>
+        <v>29500000</v>
       </c>
       <c r="BM5" t="n">
-        <v>17700000</v>
+        <v>29500000</v>
       </c>
       <c r="BN5" t="n">
-        <v>137900000</v>
+        <v>186800000</v>
       </c>
       <c r="BO5" t="n">
-        <v>-4900000</v>
+        <v>-5600000</v>
       </c>
       <c r="BP5" t="n">
-        <v>142800000</v>
+        <v>192400000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>36100000</v>
+        <v>62000000</v>
       </c>
       <c r="BR5" t="n">
-        <v>36100000</v>
+        <v>62000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>152638105</v>
+      </c>
+      <c r="C6" t="n">
+        <v>152638105</v>
+      </c>
+      <c r="D6" t="n">
+        <v>191300000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>332900000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>502000000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1231400000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>93900000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>502000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>78100000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>976600000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1037800000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>980000000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3400000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>976600000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>450400000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>170800000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>390800000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>390800000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>933000000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>247100000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>68100000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>9900000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>120100000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>58900000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>61200000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>685900000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>118400000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>212800000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>19200000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>193600000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>264700000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>260700000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1913000000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1133200000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10900000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>163800000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>41100000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>474600000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>229300000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>245300000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>438400000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-985600000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1424000000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18500000</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>1021800000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>383700000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>779800000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="n">
+        <v>7700000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>451000000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>123600000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>60300000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>267100000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>31000000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>32300000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>193500000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>-4800000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>198300000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>63500000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>63500000</v>
       </c>
     </row>
   </sheetData>
@@ -2523,7 +2666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN5"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2725,460 +2868,514 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>37500000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-148500000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>175700000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>70800000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-64200000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>62000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="n">
-        <v>90100000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>800000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-28900000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>41300000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1700000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-19000000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-21400000</v>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
-        <v>70800000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>70800000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>27200000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>27200000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-148500000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>175700000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-171900000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>76200000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-183100000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-183100000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-64200000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>101700000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-23700000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-10800000</v>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>27700000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>33000000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>104100000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>104100000</v>
-      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="n">
-        <v>-700000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>41900000</v>
-      </c>
+        <v>-200000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>73800000</v>
+        <v>1800000</v>
       </c>
       <c r="C3" t="n">
-        <v>-9100000</v>
+        <v>-20000000</v>
       </c>
       <c r="D3" t="n">
-        <v>55900000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>89500000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-65000000</v>
+        <v>-55900000</v>
       </c>
       <c r="G3" t="n">
-        <v>90100000</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>54900000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>600000</v>
+      </c>
       <c r="I3" t="n">
-        <v>54900000</v>
+        <v>36100000</v>
       </c>
       <c r="J3" t="n">
-        <v>-1100000</v>
+        <v>100000</v>
       </c>
       <c r="K3" t="n">
-        <v>36300000</v>
+        <v>18100000</v>
       </c>
       <c r="L3" t="n">
-        <v>-4600000</v>
+        <v>27600000</v>
       </c>
       <c r="M3" t="n">
-        <v>-1600000</v>
+        <v>-2700000</v>
       </c>
       <c r="N3" t="n">
-        <v>-15600000</v>
+        <v>-6700000</v>
       </c>
       <c r="O3" t="n">
-        <v>-18900000</v>
+        <v>-18200000</v>
       </c>
       <c r="P3" t="n">
-        <v>-18900000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+        <v>-18200000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>46800000</v>
+        <v>69500000</v>
       </c>
       <c r="T3" t="n">
-        <v>46800000</v>
+        <v>69500000</v>
       </c>
       <c r="U3" t="n">
-        <v>-9100000</v>
+        <v>-20000000</v>
       </c>
       <c r="V3" t="n">
-        <v>55900000</v>
+        <v>89500000</v>
       </c>
       <c r="W3" t="n">
-        <v>-97900000</v>
+        <v>-67200000</v>
       </c>
       <c r="X3" t="n">
-        <v>-1600000</v>
+        <v>-2100000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-200000</v>
+        <v>-3800000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-200000</v>
+        <v>-3800000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-31100000</v>
+        <v>-5400000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-31100000</v>
+        <v>-5400000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-65000000</v>
+        <v>-55900000</v>
       </c>
       <c r="AD3" t="n">
-        <v>138800000</v>
+        <v>57700000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-21600000</v>
+        <v>-9900000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-64700000</v>
-      </c>
-      <c r="AG3" t="inlineStr"/>
+        <v>-108400000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>32900000</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-9400000</v>
+        <v>-65700000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-18200000</v>
+        <v>-55400000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-500000</v>
+        <v>700000</v>
       </c>
       <c r="AK3" t="n">
-        <v>108700000</v>
+        <v>93600000</v>
       </c>
       <c r="AL3" t="n">
-        <v>108700000</v>
-      </c>
-      <c r="AM3" t="inlineStr"/>
+        <v>93600000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>400000</v>
+      </c>
       <c r="AN3" t="n">
-        <v>123500000</v>
+        <v>97600000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1800000</v>
+        <v>73800000</v>
       </c>
       <c r="C4" t="n">
-        <v>-20000000</v>
+        <v>-9100000</v>
       </c>
       <c r="D4" t="n">
-        <v>89500000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>55900000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-55900000</v>
+        <v>-65000000</v>
       </c>
       <c r="G4" t="n">
+        <v>90100000</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
         <v>54900000</v>
       </c>
-      <c r="H4" t="n">
-        <v>600000</v>
-      </c>
-      <c r="I4" t="n">
-        <v>36100000</v>
-      </c>
       <c r="J4" t="n">
-        <v>100000</v>
+        <v>-1100000</v>
       </c>
       <c r="K4" t="n">
-        <v>18100000</v>
+        <v>36300000</v>
       </c>
       <c r="L4" t="n">
-        <v>27600000</v>
+        <v>-4600000</v>
       </c>
       <c r="M4" t="n">
-        <v>-2700000</v>
+        <v>-1600000</v>
       </c>
       <c r="N4" t="n">
-        <v>-6700000</v>
+        <v>-15600000</v>
       </c>
       <c r="O4" t="n">
+        <v>-18900000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-18900000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>46800000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>46800000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-9100000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>55900000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>-97900000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>-1600000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-31100000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>-31100000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-65000000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>138800000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>-21600000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-64700000</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>-9400000</v>
+      </c>
+      <c r="AI4" t="n">
         <v>-18200000</v>
       </c>
-      <c r="P4" t="n">
-        <v>-18200000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>69500000</v>
-      </c>
-      <c r="T4" t="n">
-        <v>69500000</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-20000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>89500000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>-67200000</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2100000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>-3800000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-3800000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-5400000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>-5400000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-55900000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>57700000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>-9900000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-108400000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>32900000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>-65700000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>-55400000</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>700000</v>
+        <v>-500000</v>
       </c>
       <c r="AK4" t="n">
-        <v>93600000</v>
+        <v>108700000</v>
       </c>
       <c r="AL4" t="n">
-        <v>93600000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>400000</v>
-      </c>
+        <v>108700000</v>
+      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="n">
-        <v>97600000</v>
+        <v>123500000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>31600000</v>
+        <v>37500000</v>
       </c>
       <c r="C5" t="n">
-        <v>-50800000</v>
+        <v>-148500000</v>
       </c>
       <c r="D5" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>175700000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70800000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-61700000</v>
+        <v>-64200000</v>
       </c>
       <c r="G5" t="n">
-        <v>36100000</v>
+        <v>62000000</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>64700000</v>
+        <v>90100000</v>
       </c>
       <c r="J5" t="n">
-        <v>1400000</v>
+        <v>800000</v>
       </c>
       <c r="K5" t="n">
-        <v>-30000000</v>
+        <v>-28900000</v>
       </c>
       <c r="L5" t="n">
-        <v>-56100000</v>
+        <v>41300000</v>
       </c>
       <c r="M5" t="n">
-        <v>-100000</v>
+        <v>1700000</v>
       </c>
       <c r="N5" t="n">
-        <v>-4600000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>-19000000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-21400000</v>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="n">
+        <v>70800000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>70800000</v>
+      </c>
       <c r="S5" t="n">
-        <v>-35800000</v>
+        <v>27200000</v>
       </c>
       <c r="T5" t="n">
-        <v>-35800000</v>
+        <v>27200000</v>
       </c>
       <c r="U5" t="n">
-        <v>-50800000</v>
+        <v>-148500000</v>
       </c>
       <c r="V5" t="n">
-        <v>15000000</v>
+        <v>175700000</v>
       </c>
       <c r="W5" t="n">
-        <v>-67200000</v>
+        <v>-171900000</v>
       </c>
       <c r="X5" t="n">
-        <v>900000</v>
+        <v>76200000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-5800000</v>
+        <v>-800000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-5800000</v>
+        <v>-800000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-600000</v>
+        <v>-183100000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-600000</v>
+        <v>-183100000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-61700000</v>
+        <v>-64200000</v>
       </c>
       <c r="AD5" t="n">
-        <v>93300000</v>
+        <v>101700000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-4300000</v>
+        <v>-23700000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-25600000</v>
+        <v>-10800000</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-94100000</v>
+        <v>27700000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-25200000</v>
+        <v>33000000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-1200000</v>
+        <v>-800000</v>
       </c>
       <c r="AK5" t="n">
-        <v>89000000</v>
+        <v>104100000</v>
       </c>
       <c r="AL5" t="n">
-        <v>89000000</v>
+        <v>104100000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-200000</v>
+        <v>-700000</v>
       </c>
       <c r="AN5" t="n">
-        <v>34100000</v>
+        <v>41900000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>61300000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-140600000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>181300000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>127500000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-82100000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>63500000</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-2200000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>104100000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-20200000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-23600000</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="n">
+        <v>127500000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>127500000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>40700000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>40700000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-140600000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>181300000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-243800000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-163700000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-163700000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>-82100000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>143400000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-15500000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>11900000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>25300000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-13800000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-19300000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>95700000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>95700000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>73900000</v>
       </c>
     </row>
   </sheetData>
@@ -3192,7 +3389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU2"/>
+  <dimension ref="A1:EQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3373,580 +3570,560 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>dividendRate</t>
+          <t>beta</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>dividendYield</t>
+          <t>trailingPE</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>exDividendDate</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>payoutRatio</t>
+          <t>regularMarketVolume</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>beta</t>
+          <t>averageVolume</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>trailingPE</t>
+          <t>averageVolume10days</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>averageDailyVolume10Day</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>regularMarketVolume</t>
+          <t>bid</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>averageVolume</t>
+          <t>ask</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>averageVolume10days</t>
+          <t>marketCap</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>averageDailyVolume10Day</t>
+          <t>nonDilutedMarketCap</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>bid</t>
+          <t>fiftyTwoWeekLow</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>ask</t>
+          <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>marketCap</t>
+          <t>allTimeHigh</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>nonDilutedMarketCap</t>
+          <t>allTimeLow</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekLow</t>
+          <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>fiftyTwoWeekHigh</t>
+          <t>fiftyDayAverage</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>allTimeHigh</t>
+          <t>twoHundredDayAverage</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>allTimeLow</t>
+          <t>trailingAnnualDividendRate</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>priceToSalesTrailing12Months</t>
+          <t>trailingAnnualDividendYield</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>fiftyDayAverage</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>twoHundredDayAverage</t>
+          <t>tradeable</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendRate</t>
+          <t>enterpriseValue</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>trailingAnnualDividendYield</t>
+          <t>profitMargins</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>floatShares</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>tradeable</t>
+          <t>sharesOutstanding</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>enterpriseValue</t>
+          <t>heldPercentInsiders</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>profitMargins</t>
+          <t>heldPercentInstitutions</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>floatShares</t>
+          <t>impliedSharesOutstanding</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>sharesOutstanding</t>
+          <t>bookValue</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>heldPercentInsiders</t>
+          <t>priceToBook</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>heldPercentInstitutions</t>
+          <t>lastFiscalYearEnd</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>impliedSharesOutstanding</t>
+          <t>nextFiscalYearEnd</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
         <is>
-          <t>bookValue</t>
+          <t>mostRecentQuarter</t>
         </is>
       </c>
       <c r="BR1" t="inlineStr">
         <is>
-          <t>priceToBook</t>
+          <t>netIncomeToCommon</t>
         </is>
       </c>
       <c r="BS1" t="inlineStr">
         <is>
-          <t>lastFiscalYearEnd</t>
+          <t>trailingEps</t>
         </is>
       </c>
       <c r="BT1" t="inlineStr">
         <is>
-          <t>nextFiscalYearEnd</t>
+          <t>enterpriseToRevenue</t>
         </is>
       </c>
       <c r="BU1" t="inlineStr">
         <is>
-          <t>mostRecentQuarter</t>
+          <t>enterpriseToEbitda</t>
         </is>
       </c>
       <c r="BV1" t="inlineStr">
         <is>
-          <t>netIncomeToCommon</t>
+          <t>52WeekChange</t>
         </is>
       </c>
       <c r="BW1" t="inlineStr">
         <is>
-          <t>trailingEps</t>
+          <t>SandP52WeekChange</t>
         </is>
       </c>
       <c r="BX1" t="inlineStr">
         <is>
-          <t>enterpriseToRevenue</t>
+          <t>lastDividendValue</t>
         </is>
       </c>
       <c r="BY1" t="inlineStr">
         <is>
-          <t>enterpriseToEbitda</t>
+          <t>lastDividendDate</t>
         </is>
       </c>
       <c r="BZ1" t="inlineStr">
         <is>
-          <t>52WeekChange</t>
+          <t>quoteType</t>
         </is>
       </c>
       <c r="CA1" t="inlineStr">
         <is>
-          <t>SandP52WeekChange</t>
+          <t>currentPrice</t>
         </is>
       </c>
       <c r="CB1" t="inlineStr">
         <is>
-          <t>lastDividendValue</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CC1" t="inlineStr">
         <is>
-          <t>lastDividendDate</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CD1" t="inlineStr">
         <is>
-          <t>quoteType</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CE1" t="inlineStr">
         <is>
-          <t>currentPrice</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CF1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CG1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CH1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CI1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CJ1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CK1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="CL1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="CM1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="CN1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="CO1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>language</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>region</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>exchange</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>messageBoardId</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>exchangeTimezoneName</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>exchangeTimezoneShortName</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
       <c r="DQ1" t="inlineStr">
         <is>
-          <t>marketState</t>
+          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="DR1" t="inlineStr">
         <is>
-          <t>shortName</t>
+          <t>fiftyDayAverageChange</t>
         </is>
       </c>
       <c r="DS1" t="inlineStr">
         <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
       <c r="EQ1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3968,10 +4145,8 @@
           <t>Cologne</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>51149</t>
-        </is>
+      <c r="D2" t="n">
+        <v>51149</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -4052,7 +4227,7 @@
         <v>5</v>
       </c>
       <c r="W2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="X2" t="n">
         <v>1767139200</v>
@@ -4069,419 +4244,407 @@
         <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.17</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
       <c r="AE2" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
       <c r="AF2" t="n">
-        <v>10.17</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
       <c r="AH2" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
       <c r="AI2" t="n">
-        <v>10.27</v>
+        <v>9.84</v>
       </c>
       <c r="AJ2" t="n">
+        <v>1.842</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>17.258621</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>77</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>910</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1527907584</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1514170001</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.995</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.178</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0.7328797</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>10.0678</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>9.634225000000001</v>
+      </c>
+      <c r="BB2" t="n">
         <v>0.18</v>
       </c>
-      <c r="AK2" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="BC2" t="n">
+        <v>0.018054163</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="BE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>1922210688</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.04082</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>147735714</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>152638105</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>152638105</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>6.537</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.5312835</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1767139200</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1798675200</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1774915200</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>85100000</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>0.922</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>12.166</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0.42530382</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.24487448</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BY2" t="n">
         <v>1778716800</v>
       </c>
-      <c r="AM2" t="n">
-        <v>0.6071</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.839</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>35.714287</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>321</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>321</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>965</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>92</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>92</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11.37</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1526381056</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1546224003</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.178</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0.73214746</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>9.904</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>9.610225</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.017699115</v>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>EQUITY</t>
+        </is>
+      </c>
+      <c r="CA2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CC2" t="n">
+        <v>64500000</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>158000000</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>449600000</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>0.441</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>2084800000</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>44.621</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>14.302</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.02702</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>0.09231</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>454200000</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>3952000</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>118400000</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>0.21786</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>0.07579</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0.05491</v>
+      </c>
+      <c r="CU2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="BI2" t="b">
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>1DEZ.MI</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>en-US</t>
+        </is>
+      </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>Delayed Quote</t>
+        </is>
+      </c>
+      <c r="DA2" t="b">
         <v>0</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>1924514304</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.04082</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>147735714</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>152638105</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0.0346</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.44941002</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>152638105</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6.537</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1.5297537</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>1767139200</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1798675200</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1774915200</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>85100000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>12.18</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0.31298697</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0.27449715</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>1778716800</v>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>EQUITY</t>
-        </is>
-      </c>
-      <c r="CE2" t="n">
-        <v>10</v>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="CG2" t="n">
-        <v>64500000</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>158000000</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>449600000</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>0.441</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2084800000</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>44.621</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>14.302</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>0.02702</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>0.09231</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>454200000</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>3952000</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>118400000</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>0.21786</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>0.07579</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>0.05491</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>EUR</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>1DEZ.MI</t>
-        </is>
-      </c>
-      <c r="DA2" t="inlineStr">
-        <is>
-          <t>en-US</t>
-        </is>
-      </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>Delayed Quote</t>
-        </is>
-      </c>
-      <c r="DE2" t="b">
+          <t>finmb_618582</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DI2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DJ2" t="n">
+        <v>0.4012032</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>10.01</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DM2" t="n">
+        <v>1781852420</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>DEUTZ</t>
+        </is>
+      </c>
+      <c r="DP2" t="inlineStr">
         <is>
           <t>DEUTZ Aktiengesellschaft</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>1780414680</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>finmb_618582</t>
-        </is>
-      </c>
-      <c r="DL2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="DP2" t="b">
+      <c r="DQ2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.05779934</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>-0.00574101</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.37577534</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.03900421</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>20</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>DEUTZ</t>
-        </is>
-      </c>
-      <c r="DS2" t="b">
+      <c r="DY2" t="b">
         <v>0</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="DZ2" t="n">
         <v>1701676800000</v>
       </c>
-      <c r="DU2" t="n">
-        <v>-0.17000008</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>10.27 - 10.27</t>
-        </is>
-      </c>
-      <c r="DW2" t="inlineStr">
+      <c r="EA2" t="n">
+        <v>0.03999996</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>9.84 - 9.84</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="DX2" t="n">
-        <v>965</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>0.44927534</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>6.9 - 12.09</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>-2.0900002</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.17287014</v>
-      </c>
       <c r="ED2" t="n">
-        <v>31.298697</v>
+        <v>910</v>
       </c>
       <c r="EE2" t="n">
+        <v>3.0150003</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0.43102223</v>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>6.995 - 12.09</t>
+        </is>
+      </c>
+      <c r="EH2" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.172043</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>42.53038</v>
+      </c>
+      <c r="EK2" t="n">
         <v>1786030200</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EL2" t="n">
         <v>1786030200</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EM2" t="n">
         <v>1786030200</v>
       </c>
-      <c r="EH2" t="n">
+      <c r="EN2" t="n">
         <v>1786013940</v>
       </c>
-      <c r="EI2" t="n">
+      <c r="EO2" t="n">
         <v>1786013940</v>
       </c>
-      <c r="EJ2" t="b">
+      <c r="EP2" t="b">
         <v>0</v>
       </c>
-      <c r="EK2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>0.09599972</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>0.009693024999999999</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>0.38977528</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>0.040558394</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>20</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ER2" t="b">
-        <v>0</v>
-      </c>
-      <c r="ES2" t="n">
-        <v>-1.6715838</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>10</v>
-      </c>
-      <c r="EU2" t="inlineStr"/>
+      <c r="EQ2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
